--- a/01-文档/RTM_康养系统_老师模板版.xlsx
+++ b/01-文档/RTM_康养系统_老师模板版.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -992,7 +992,11 @@
       <c r="H39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n"/>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="n"/>
       <c r="D40" s="1" t="n"/>
@@ -1000,6 +1004,11 @@
       <c r="F40" s="1" t="n"/>
       <c r="G40" s="1" t="n"/>
       <c r="H40" s="1" t="n"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>组长姓名</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1043,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1581,6 +1590,71 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>补充任务分工：丘宇乾(COD 后端), 梁霁鸣(PD 原型/老人端/家属端 RTM), 周彦龙(UT 护工端/管理员 RTM+ 测试)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>设计用RTM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>42</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>42</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1629,22 +1703,16 @@
           <t>基于 AI 智能体的康养系统</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
           <t>PM:吴剑光</t>
         </is>
       </c>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
       <c r="I2" s="9" t="inlineStr">
         <is>
           <t>担当:具体参与设计的成员名单</t>
         </is>
       </c>
-      <c r="J2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -1732,11 +1800,15 @@
         </is>
       </c>
       <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H5" s="13" t="n"/>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -1764,11 +1836,15 @@
         </is>
       </c>
       <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H6" s="13" t="n"/>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -1796,11 +1872,15 @@
         </is>
       </c>
       <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -1828,11 +1908,15 @@
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1860,11 +1944,15 @@
         </is>
       </c>
       <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -1896,11 +1984,15 @@
         </is>
       </c>
       <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -1932,15 +2024,19 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标1，标题"健康首页"，黑体，字号22px，加粗，颜色#2d6a4f，左对齐；图标2，今日健康卡片动态显示血压/心率/血糖，字号20px，正常值色#2d6a4f，超标值红#e74c3c</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G11" s="13" t="n"/>
       <c r="H11" s="13" t="n"/>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -1968,15 +2064,19 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标3，大按钮"我的档案"，字号20px，加粗，白字，背景#52b788，高度≥48px，动作：点击直达健康档案查看</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G12" s="13" t="n"/>
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -2000,15 +2100,19 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标4，大按钮"问一问 AI"，字号20px，加粗，白字，背景#2d6a4f，高度≥48px，动作：点击进入AI咨询页</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G13" s="13" t="n"/>
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -2032,15 +2136,19 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标5，大按钮"我的预警"，字号20px，加粗，白字，背景#e67e22，存在未处理预警时右上角红色角标#e74c3c，动作：点击直达预警中心</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n"/>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -2068,15 +2176,19 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标6，"🔊 朗读"按钮，字号16px，边框#2d6a4f，动作：点击调用网页朗读（Web Speech API）播报页面关键文字，再点停止</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G15" s="13" t="n"/>
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -2100,15 +2212,19 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标15，登录后弹出用药/健康打卡提醒卡片，字号18px，背景#f0faf3浅绿，动作：点击"知道了"关闭，每日仅提醒一次</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G16" s="13" t="n"/>
       <c r="H16" s="13" t="n"/>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -2140,15 +2256,19 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标7，以卡片列表展示本账号多份档案（姓名/年龄/照片/慢病标签），字号18px，加粗，动作：点击卡片即切换并查看对应档案详情</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G17" s="13" t="n"/>
       <c r="H17" s="13" t="n"/>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -2176,15 +2296,19 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标8，按钮"新建档案"，白字，背景#52b788，字号18px，动作：弹出表单填写姓名/年龄/病史/慢病标签，必填校验通过后保存并生成新档案</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G18" s="13" t="n"/>
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
@@ -2208,15 +2332,19 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标9，编辑按钮"保存"白字背景#2d6a4f；图标10，删除按钮文字红色#e74c3c，动作：编辑后保存即时生效；删除前弹出二次确认，确认后删除并解除绑定</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G19" s="13" t="n"/>
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -2248,15 +2376,19 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标11，标签"血压"字号18px，输入收缩/舒张压数值，动作：范围校验（收缩90~200 / 舒张60~130），越界红色#e74c3c提示</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G20" s="13" t="n"/>
       <c r="H20" s="13" t="n"/>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -2280,15 +2412,19 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标12，标签"心率 / 血糖"字号18px，动作：录入数值，心率40~200、血糖2.0~20.0 范围校验，越界提示</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G21" s="13" t="n"/>
       <c r="H21" s="13" t="n"/>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -2312,15 +2448,19 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>参照图2，图标13，按钮"保存指标"白字背景#2d6a4f字号18px，动作：写入统一健康记录表并触发预警检测；图14，ECharts近30天趋势折线，正常点色#2d6a4f，超阈值点红#e74c3c高亮，支持切换指标类型</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G22" s="13" t="n"/>
       <c r="H22" s="13" t="n"/>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
@@ -2356,11 +2496,15 @@
         </is>
       </c>
       <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H23" s="13" t="n"/>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -2392,11 +2536,15 @@
         </is>
       </c>
       <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H24" s="13" t="n"/>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -2424,11 +2572,15 @@
         </is>
       </c>
       <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H25" s="13" t="n"/>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -2460,11 +2612,15 @@
         </is>
       </c>
       <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
@@ -2492,11 +2648,15 @@
         </is>
       </c>
       <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H27" s="13" t="n"/>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾/梁霁鸣/周彦龙</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
@@ -2528,11 +2688,15 @@
         </is>
       </c>
       <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H28" s="13" t="n"/>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -2568,11 +2732,15 @@
         </is>
       </c>
       <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H29" s="13" t="n"/>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -2600,11 +2768,15 @@
         </is>
       </c>
       <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H30" s="13" t="n"/>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -2636,11 +2808,15 @@
         </is>
       </c>
       <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H31" s="13" t="n"/>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
@@ -2672,11 +2848,15 @@
         </is>
       </c>
       <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H32" s="13" t="n"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
@@ -2708,11 +2888,15 @@
         </is>
       </c>
       <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H33" s="13" t="n"/>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
@@ -2744,11 +2928,15 @@
         </is>
       </c>
       <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>丘宇乾</t>
+        </is>
+      </c>
       <c r="H34" s="13" t="n"/>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>丘宇乾</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
@@ -2780,15 +2968,19 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>参照图5，图标1，标题"家属端"，黑体，字号20px，加粗，颜色#2d6a4f，左对齐；图标2，"添加老人"按钮白字背景#52b788字号18px，动作：通过手机号/邀请码绑定并代管多位老人，可解绑，解绑后权限立即失效</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G35" s="13" t="n"/>
       <c r="H35" s="13" t="n"/>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2816,15 +3008,19 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>参照图5，图标3，以卡片列表展示所有代管老人，含头衔/今日关键指标/最近预警数量，字号16px，正常绿、有预警红角标，动作：点击切换查看该老人健康概况与档案</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G36" s="13" t="n"/>
       <c r="H36" s="13" t="n"/>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
@@ -2848,15 +3044,19 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>参照图5，图标4，"健康趋势"图表入口，ECharts展示代管老人近30天趋势；图标5，"代录数据"按钮白字背景#2d6a4f，动作：在家属端为老人录入血压/心率等健康指标</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G37" s="13" t="n"/>
       <c r="H37" s="13" t="n"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -2884,15 +3084,19 @@
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>参照图5，图标6，接收并查看代管老人全部预警，高优先级置顶红#e74c3c；图标7，"代问 AI"按钮白字背景#2d6a4f，动作：以所选老人档案发起AI咨询</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G38" s="13" t="n"/>
       <c r="H38" s="13" t="n"/>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -2916,15 +3120,19 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>参照图5，图标8，按钮"确认已处理/已联系老人"，字号16px，白字背景#52b788，动作：登记处理状态供追溯；图标9，家属端通知中心汇总所有老人预警，已读/未读状态</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n"/>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>梁霁鸣</t>
+        </is>
+      </c>
       <c r="G39" s="13" t="n"/>
       <c r="H39" s="13" t="n"/>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>梁霁鸣</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -2956,15 +3164,23 @@
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>参照图6，图标1，标题"护工端"，黑体，字号20px，加粗，颜色#2d6a4f，左对齐；图标2，负责老人列表按状态分色标识：正常绿#2d6a4f/关注橙#e67e22/异常红#e74c3c，高风险老人置顶，动作：点击进入详情</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
@@ -2988,15 +3204,23 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>参照图6，图标3，工作台汇总负责老人今日待办（未处理预警/健康打卡），字号16px，异常优先排序；图标4，支持按状态/时段筛选老人</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -3024,15 +3248,23 @@
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>参照图6，图标5，查看负责老人预警列表与详情（指标值/阈值/趋势），字号16px，处理状态标签；图标6，"登记处理结果"按钮白字背景#2d6a4f，动作：填写处理结论并留痕，供追溯</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
@@ -3064,15 +3296,23 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>参照图7，图标1，标题"系统后台"，黑体，字号20px，加粗，颜色#2d6a4f，左对齐；图标2，用户列表含角色/状态，支持启用/禁用，动作：禁用后该用户不可登录；图标3，角色分配与权限维护</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -3100,15 +3340,23 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>参照图7，图标4，"预警规则"配置表单，各指标阈值与风险等级（入sys_config，不写死），字号16px，动作：修改后预警逻辑即时生效</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
@@ -3136,15 +3384,23 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>参照图7，图标5，"知识库管理"，支持常见问答/健康文章增删改（仅管理员可改他人只读），字号16px，动作：条目更新后重建向量索引供AI咨询RAG检索</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -3172,15 +3428,23 @@
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>参照图7，图标6，统计看板展示用户数/咨询次数/预警发生与处理数，ECharts图表，字号16px；动作：支持按日/周/月筛选并导出报表</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n"/>
+          <t>周彦龙</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>周彦龙</t>
+        </is>
+      </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>[组员A/B/C]</t>
+          <t>周彦龙</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
